--- a/testdata/realdata/cable_segments.xlsx
+++ b/testdata/realdata/cable_segments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Z端接头盒</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>SB-HDQ-01-Z</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>SB-HDQ-02-Z</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +538,11 @@
           <t>SB-HDQ-03-Z</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +570,11 @@
           <t>SB-HDQ-04-Z</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +602,11 @@
           <t>SB-HM-01-Z</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +634,11 @@
           <t>SB-HM-02-Z</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +666,11 @@
           <t>SB-HM-03-Z</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +698,11 @@
           <t>SB-HJ-01-Z</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +730,11 @@
           <t>SB-HJ-02-Z</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +762,11 @@
           <t>SB-HJ-03-Z</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +794,11 @@
           <t>SB-HJ-04-Z</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +826,11 @@
           <t>SB-JM-01-Z</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +858,11 @@
           <t>SB-JM-02-Z</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +890,11 @@
           <t>SB-JM-03-Z</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +922,11 @@
           <t>SB-JM-04-Z</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -874,6 +954,11 @@
           <t>SB-QJ-01-Z</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -901,6 +986,11 @@
           <t>SB-QJ-02-Z</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +1018,11 @@
           <t>SB-QJ-03-Z</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1050,11 @@
           <t>SB-JM2-01-Z</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1082,11 @@
           <t>SB-JM2-02-Z</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,6 +1114,11 @@
           <t>SB-HY-01-Z</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1036,6 +1146,11 @@
           <t>SB-HY-02-Z</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1061,6 +1176,11 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>SB-HY-03-Z</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
